--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_Phan_02_21_Cau.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -690,7 +690,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một người khác phải rerun mà không hỏi người sửa.</t>
+          <t>Một quy trình làm sạch dữ liệu được chứng minh là có thể tái lập (replayable) khi thỏa mãn: (a) Dữ liệu thô ban đầu và phiên bản của nó được lưu trữ bất biến; (b) Toàn bộ các quy tắc làm sạch nằm trong mã nguồn và hợp đồng dữ liệu có quản lý phiên bản; (c) Cùng một dữ liệu đầu vào và bộ quy tắc luôn tạo ra cùng một kết quả xác định; (d) Có dấu vết lineage ghi nhận đầy đủ trạng thái trước và sau khi xử lý của từng lần chạy.</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1051,7 +1051,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Reviewer phải biết record nào, từ đâu, vì sao và làm tiếp gì.</t>
+          <t>Một bản ghi trong vùng cách ly (quarantine entry) cần lưu giữ đầy đủ để có thể khắc phục hoặc phục vụ kiểm toán: (a) Dòng dữ liệu gốc hoặc tham chiếu bất biến tới dữ liệu gốc; (b) Quy tắc/lý do vi phạm và bằng chứng lỗi cụ thể; (c) Định danh nguồn và mã định danh lần chạy (Run ID); (d) Người chịu trách nhiệm xem xét, trạng thái xử lý và quyết định replay.</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1096,7 +1096,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng số phân vùng dự kiến làm mẫu số.</t>
+          <t>Độ bao phủ phân vùng (partition coverage) được tính bằng tỷ lệ phần trăm giữa số phân vùng thực tế xuất hiện trên tổng số phân vùng dự kiến: 228 / 240 = 19 / 20 = 0,95 = 95%.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1144,7 +1144,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ chấm rule được cung cấp.</t>
+          <t>Đối chiếu bản ghi `{age: 150, email: 'a@b', status: 'active'}` với schema đã cho: (a) Trường age=150 nằm ngoài khoảng cho phép 0..120 nên không hợp lệ; (b) Trường email='a@b' có chứa ký tự '@' nên hợp lệ theo đúng quy tắc kiểm tra đã nêu; (c) Trường status='active' thuộc tập hợp giá trị hợp lệ {active, inactive} nên hợp lệ.</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1241,7 +1241,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Consistency hỏi các phần liên quan có đồng ý theo invariant không.</t>
+          <t>Các phép kiểm tra tính nhất quán (consistency checks) trong bộ dữ liệu orders gồm: (a) Tính nhất quán trong bản ghi: `order.total = sum(line.amount)` cùng đơn vị tiền tệ; (b) Tính nhất quán tham chiếu: mọi `customer_id` đều tham chiếu tới một khách hàng tồn tại trong bảng customers; (c) Tính nhất quán giữa các biểu diễn: cùng một order_id phải có cùng trạng thái trên các view tại cùng một thời điểm. Kiểm tra email chứa @ và order.total nằm trong dải là các kiểm tra hợp lệ định dạng/miền giá trị (validity), không phải consistency.</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1286,7 +1286,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Clock dừng ở publish boundary, không ở job start.</t>
+          <t>Độ trễ dữ liệu (freshness lag) được tính từ thời điểm phát sinh sự kiện nguồn (09:00) đến ranh giới xuất bản phục vụ người dùng (09:18): 09:18 - 09:00 = 18 phút. Độ trễ 18 phút đã vượt quá mức SLA tối đa 15 phút là 3 phút.</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1383,7 +1383,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một operator phải biết check gì và làm gì khi fail.</t>
+          <t>Một hợp đồng dữ liệu (data contract) có tính thực thi cao cho validator và operator cần: (a) Định nghĩa schema chuẩn hóa, các trường bắt buộc, miền giá trị và khóa định danh; (b) Xác định rõ người sở hữu (owner) và nguồn sự thật có thẩm quyền; (c) Quy định mức độ nghiêm trọng và hậu quả xử lý cho từng loại vi phạm; (d) Khi độ mới dữ liệu chưa rõ, chỉ định rõ người ra quyết định thay vì tự ý điền giá trị ngầm định.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1492,7 +1492,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người review cần tái tạo được lý do pass/fail và biết bản ghi nào cần xử lý.</t>
+          <t>Kết quả kiểm tra kỳ vọng dữ liệu (data expectation result) cần lưu trữ đầy đủ để phục vụ kiểm toán và xử lý lỗi: (a) Tên điều khoản/chiều chất lượng và phạm vi kiểm tra của lần chạy; (b) Giá trị quan sát được kèm mẫu số tính toán; (c) Ngưỡng chấp nhận và mức độ nghiêm trọng của lỗi; (d) Bằng chứng cụ thể về các dòng dữ liệu bị lỗi hoặc lát cắt dữ liệu vi phạm. Chỉ trả về giá trị boolean false là không đủ thông tin chẩn đoán.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -1544,7 +1544,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê cả điều suite không quan sát.</t>
+          <t>Khi bộ kiểm tra đạt các tiêu chí not-null, type và range trên phân vùng của ngày hôm nay, các kết luận hợp lý là: (a) Toàn bộ các quy tắc đã triển khai đều đạt yêu cầu trên phạm vi phân vùng hôm nay; (c) Các phân vùng của những ngày khác vẫn chưa được kiểm tra; (d) Các quy tắc nghiệp vụ sâu hơn hoặc tính thẩm quyền của nguồn có thể chưa được kiểm tra trong bộ test này. Không thể suy diễn dữ liệu tương lai chắc chắn đúng hay độ chính xác bên ngoài đã được chứng minh.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1589,7 +1589,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ bản ghi mà rule đã chặn.</t>
+          <t>Độ chính xác (Precision) của quy tắc chặn lỗi: Tỷ lệ giữa số bản ghi thực sự bị lỗi (True Positives = 30) trên tổng số bản ghi mà quy tắc đã chặn (Total Predicted Positives = 40): Precision = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>
